--- a/config_sets.xlsx
+++ b/config_sets.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,11 +496,7 @@
           <t>1872</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>https://www.lego.com/cdn/cs/set/assets/blt55fbccadb7d66885/10300.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
@@ -764,11 +760,7 @@
           <t>806</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>https://www.lego.com/cdn/cs/set/assets/bltb82764353d6cd9c2/bltaa6c5faaf18aa138-11505_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
@@ -832,11 +824,7 @@
           <t>2193</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>https://www.lego.com/cdn/cs/set/assets/blta1405340d716cd20/21351_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
@@ -919,28 +907,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>45200</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kit de science Mission lunaire</t>
+          <t>Megacar Sadair's Spear de Koenigsegg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.lego.com/cdn/cs/set/assets/bltf7b7ce8f03c1660e/bltb54bf9af8b6f95a9-45200_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
+          <t>https://www.lego.com/cdn/cs/set/assets/bltdd490f7023a9625c/blt115568a63fa37862-42232_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.lego.com/fr-fr/product/45200</t>
+          <t>https://www.lego.com/fr-fr/product/42232</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -951,32 +943,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>45201</t>
+          <t>45200</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kit de science Animaux de l’Antarctique</t>
+          <t>Kit de science Mission lunaire</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.lego.com/cdn/cs/set/assets/blte5a2e0694b4165e5/blt4370f603aae1af0d-45201_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
+          <t>https://www.lego.com/cdn/cs/set/assets/bltf7b7ce8f03c1660e/bltb54bf9af8b6f95a9-45200_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.lego.com/fr-fr/product/45201</t>
+          <t>https://www.lego.com/fr-fr/product/45200</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -987,32 +975,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>80121</t>
+          <t>45201</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L’auberge traditionnelle du clair de lune</t>
+          <t>Kit de science Animaux de l’Antarctique</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1530</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.lego.com/cdn/cs/set/assets/bltfc4f59188fa9bf87/blt00132fa0deebd2ee-80121_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
+          <t>https://www.lego.com/cdn/cs/set/assets/blte5a2e0694b4165e5/blt4370f603aae1af0d-45201_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.lego.com/fr-fr/product/80121</t>
+          <t>https://www.lego.com/fr-fr/product/45201</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1020,6 +1004,38 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>80121</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>L’auberge traditionnelle du clair de lune</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.lego.com/cdn/cs/set/assets/bltfc4f59188fa9bf87/blt00132fa0deebd2ee-80121_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.lego.com/fr-fr/product/80121</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config_sets.xlsx
+++ b/config_sets.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -747,28 +747,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>11383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Les champignons des bois</t>
+          <t>Le manoir du maire</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.lego.com/cdn/cs/set/assets/bltb82764353d6cd9c2/bltaa6c5faaf18aa138-11505_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
+          <t>https://www.lego.com/cdn/cs/set/assets/bltaf15f7318ac0ba98/blt21fb8295f9caaf81-11383_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.lego.com/fr-fr/product/11505</t>
+          <t>https://www.lego.com/fr-fr/product/11383</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -843,28 +847,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>31218</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Les cerisiers en fleurs</t>
+          <t>Megacar Sadair's Spear de Koenigsegg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.lego.com/cdn/cs/set/assets/blt3f6cace2ff7687c6/31218_Prod_en-gb.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
+          <t>https://www.lego.com/cdn/cs/set/assets/bltdd490f7023a9625c/blt115568a63fa37862-42232_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.lego.com/fr-fr/product/31218</t>
+          <t>https://www.lego.com/fr-fr/product/42232</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -875,28 +879,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>42222</t>
+          <t>45200</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hypercar Bugatti Chiron Pur Sport</t>
+          <t>Kit de science Mission lunaire</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>519</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.lego.com/cdn/cs/set/assets/blt0a9009b95130ef89/42222_Prod_en-gb.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
+          <t>https://www.lego.com/cdn/cs/set/assets/bltf7b7ce8f03c1660e/bltb54bf9af8b6f95a9-45200_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.lego.com/fr-fr/product/42222</t>
+          <t>https://www.lego.com/fr-fr/product/45200</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -907,32 +911,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>45201</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Megacar Sadair's Spear de Koenigsegg</t>
+          <t>Kit de science Animaux de l’Antarctique</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4104</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.lego.com/cdn/cs/set/assets/bltdd490f7023a9625c/blt115568a63fa37862-42232_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
+          <t>https://www.lego.com/cdn/cs/set/assets/blte5a2e0694b4165e5/blt4370f603aae1af0d-45201_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.lego.com/fr-fr/product/42232</t>
+          <t>https://www.lego.com/fr-fr/product/45201</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -943,28 +943,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>45200</t>
+          <t>80121</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kit de science Mission lunaire</t>
+          <t>L’auberge traditionnelle du clair de lune</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.lego.com/cdn/cs/set/assets/bltf7b7ce8f03c1660e/bltb54bf9af8b6f95a9-45200_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
+          <t>https://www.lego.com/cdn/cs/set/assets/bltfc4f59188fa9bf87/blt00132fa0deebd2ee-80121_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.lego.com/fr-fr/product/45200</t>
+          <t>https://www.lego.com/fr-fr/product/80121</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -972,70 +972,6 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>45201</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Kit de science Animaux de l’Antarctique</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://www.lego.com/cdn/cs/set/assets/blte5a2e0694b4165e5/blt4370f603aae1af0d-45201_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://www.lego.com/fr-fr/product/45201</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>80121</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>L’auberge traditionnelle du clair de lune</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1530</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://www.lego.com/cdn/cs/set/assets/bltfc4f59188fa9bf87/blt00132fa0deebd2ee-80121_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://www.lego.com/fr-fr/product/80121</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config_sets.xlsx
+++ b/config_sets.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,58 +413,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID_Set</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nom_Set</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>nbPieces</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Collection</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Image_URL</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>URL_Lego</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>URL_Auchan</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>URL_Leclerc</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>URL_Carrefour</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>URL_AvenueDeLaBrique</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Marque</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Prix_Alerte</t>
         </is>
       </c>
     </row>
@@ -511,6 +509,12 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -543,6 +547,12 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -575,6 +585,12 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -607,6 +623,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -643,6 +665,12 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -679,6 +707,12 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -711,6 +745,12 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -743,6 +783,12 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -760,11 +806,7 @@
           <t>1420</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>https://www.lego.com/cdn/cs/set/assets/bltaf15f7318ac0ba98/blt21fb8295f9caaf81-11383_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=528&amp;height=528&amp;dpr=1</t>
@@ -779,6 +821,12 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,6 +859,12 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -843,6 +897,12 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -875,6 +935,12 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -907,6 +973,12 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -939,6 +1011,12 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -971,6 +1049,12 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>LEGO</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
